--- a/04_모델산출물/v7_제형모델/지표_제형모델.xlsx
+++ b/04_모델산출물/v7_제형모델/지표_제형모델.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제형모델" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'제형모델'!$A$1:$AK$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'제형모델'!$A$1:$AL$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,2198 +415,3275 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AL25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>대표</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>endpoint</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>관할</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>피처</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>결측처리</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>CT</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>양성</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>유병률</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>roc_auc</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>roc_auc_sd</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>pr_auc</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>pr_auc_sd</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>f1_pos</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>f1_pos_sd</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>f1_neg</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>f1_macro</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>specificity</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>MCC</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>BA</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>accuracy</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>tp</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>fn</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>tn</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>F1_최적임계값_참고_seed4</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>최적임계값_참고_seed4</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>f1_neg_sd</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>f1_macro_sd</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>precision_sd</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>recall_sd</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>specificity_sd</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>MCC_sd</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>BA_sd</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>accuracy_sd</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>UN_GHS+K_REACH+US_OSHA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>nan0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1044</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>713</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>0.6745</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.0097</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.8003</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.0107</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0.7992</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.0054</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.4053</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>0.6022</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>0.7356</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>0.8749</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>0.3227</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>0.2354</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>0.5988</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>0.6998</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>623.8</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>224.2</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>89.2</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
         <v>106.8</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AC2" t="n">
         <v>0.8191000000000001</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
         <v>0.347</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
         <v>0.0169</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AF2" t="n">
         <v>0.0108</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>0.0051</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>0.0073</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AI2" t="n">
         <v>0.0153</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AJ2" t="n">
         <v>0.0218</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AK2" t="n">
         <v>0.0094</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
         <v>0.007900000000000001</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>UN_GHS+K_REACH+US_OSHA</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>nan0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1044</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>713</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>0.6858</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.0071</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.8123</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.0073</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>0.7977</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>0.0051</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>0.4122</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>0.605</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>0.7375</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>0.8687</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>0.3335</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>0.2372</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>0.6011</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>0.699</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>619.4</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>220.6</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>93.59999999999999</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AB3" t="n">
         <v>110.4</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AC3" t="n">
         <v>0.8201000000000001</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
         <v>0.31</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AE3" t="n">
         <v>0.0275</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AF3" t="n">
         <v>0.0156</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AG3" t="n">
         <v>0.0081</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AH3" t="n">
         <v>0.008699999999999999</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AI3" t="n">
         <v>0.0303</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AJ3" t="n">
         <v>0.0274</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AK3" t="n">
         <v>0.0136</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AL3" t="n">
         <v>0.0086</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>UN_GHS+K_REACH+US_OSHA</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>native</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1044</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>713</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>0.6677999999999999</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.0108</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.7979000000000001</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.0095</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0.7973</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>0.0027</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>0.3962</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0.5968</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0.733</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>0.8741</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>0.3142</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>0.2252</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>0.5941</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>0.6966</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>623.2</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>227</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>89.8</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AB4" t="n">
         <v>104</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AC4" t="n">
         <v>0.8187</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AD4" t="n">
         <v>0.352</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AE4" t="n">
         <v>0.0145</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AG4" t="n">
         <v>0.0041</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
         <v>0.0032</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AI4" t="n">
         <v>0.0146</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AJ4" t="n">
         <v>0.0151</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AK4" t="n">
         <v>0.0071</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AL4" t="n">
         <v>0.0047</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>UN_GHS+K_REACH+US_OSHA</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>native</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1044</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>713</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>0.6744</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.0097</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.8051</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.0112</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.8012</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>0.0037</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>0.4106</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>0.6059</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>0.7374000000000001</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.8771</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>0.3269</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0.2433</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0.602</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>0.7027</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>625.4</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>222.8</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AB5" t="n">
         <v>108.2</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
         <v>0.8209</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
         <v>0.332</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AE5" t="n">
         <v>0.0132</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AF5" t="n">
         <v>0.007</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AG5" t="n">
         <v>0.0036</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AH5" t="n">
         <v>0.009299999999999999</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AI5" t="n">
         <v>0.0165</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AJ5" t="n">
         <v>0.0121</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AK5" t="n">
         <v>0.0059</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AL5" t="n">
         <v>0.0045</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>0</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>EU_CLP</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>UN_GHS+K_REACH+US_OSHA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nan0</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1044</v>
       </c>
-      <c r="H6" t="n">
-        <v>386</v>
-      </c>
       <c r="I6" t="n">
-        <v>0.3697</v>
+        <v>713</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7423</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0049</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6523</v>
+        <v>0.0139</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0131</v>
+        <v>0.7986</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6001</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0113</v>
+        <v>0.7978</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7938</v>
+        <v>0.0026</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.697</v>
+        <v>0.3925</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6572</v>
+        <v>0.5951</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5523</v>
+        <v>0.7321</v>
       </c>
       <c r="T6" t="n">
-        <v>0.831</v>
+        <v>0.8763</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3999</v>
+        <v>0.3094</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6917</v>
+        <v>0.2236</v>
       </c>
       <c r="W6" t="n">
-        <v>0.728</v>
+        <v>0.5928</v>
       </c>
       <c r="X6" t="n">
-        <v>213.2</v>
+        <v>0.6966</v>
       </c>
       <c r="Y6" t="n">
-        <v>111.2</v>
+        <v>624.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>172.8</v>
+        <v>228.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>546.8</v>
+        <v>88.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6216</v>
+        <v>102.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.366</v>
+        <v>0.8202</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0032</v>
+        <v>0.326</v>
       </c>
       <c r="AE6" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="AF6" t="n">
         <v>0.0069</v>
       </c>
-      <c r="AF6" t="n">
-        <v>0.0066</v>
-      </c>
       <c r="AG6" t="n">
-        <v>0.0171</v>
+        <v>0.0033</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0059</v>
+        <v>0.0054</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0126</v>
+        <v>0.0133</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0072</v>
+        <v>0.0121</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.005</v>
+        <v>0.0057</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.0039</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>EU_CLP</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>UN_GHS+K_REACH+US_OSHA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>nan0</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1044</v>
       </c>
-      <c r="H7" t="n">
-        <v>386</v>
-      </c>
       <c r="I7" t="n">
-        <v>0.3697</v>
+        <v>713</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7577</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0034</v>
+        <v>0.6752</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6745</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0091</v>
+        <v>0.8058</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6096</v>
+        <v>0.0073</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0068</v>
+        <v>0.8008</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8006</v>
+        <v>0.0023</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.4152</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6725</v>
+        <v>0.608</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5575</v>
+        <v>0.7385</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8407</v>
+        <v>0.8746</v>
       </c>
       <c r="U7" t="n">
-        <v>0.417</v>
+        <v>0.3329</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6991000000000001</v>
+        <v>0.2455</v>
       </c>
       <c r="W7" t="n">
-        <v>0.736</v>
+        <v>0.6038</v>
       </c>
       <c r="X7" t="n">
-        <v>215.2</v>
+        <v>0.7029</v>
       </c>
       <c r="Y7" t="n">
-        <v>104.8</v>
+        <v>623.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>170.8</v>
+        <v>220.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>553.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6377</v>
+        <v>110.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.351</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.0028</v>
+        <v>0.34</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.0045</v>
+        <v>0.016</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0064</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0098</v>
+        <v>0.0046</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.005</v>
+        <v>0.0054</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0183</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.0045</v>
+        <v>0.0142</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0037</v>
+        <v>0.0075</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.0041</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>EU_CLP</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>native</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>nan0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1044</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>386</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>0.3697</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.7504999999999999</v>
-      </c>
       <c r="K8" t="n">
+        <v>0.7423</v>
+      </c>
+      <c r="L8" t="n">
         <v>0.0049</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.6647</v>
-      </c>
       <c r="M8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.6523</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5978</v>
+        <v>0.0131</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.6001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7942</v>
+        <v>0.0113</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.696</v>
+        <v>0.7938</v>
       </c>
       <c r="R8" t="n">
-        <v>0.659</v>
+        <v>0.697</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5472</v>
+        <v>0.6572</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8337</v>
+        <v>0.5523</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3987</v>
+        <v>0.831</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6904</v>
+        <v>0.3999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.7278</v>
+        <v>0.6917</v>
       </c>
       <c r="X8" t="n">
-        <v>211.2</v>
+        <v>0.728</v>
       </c>
       <c r="Y8" t="n">
-        <v>109.4</v>
+        <v>213.2</v>
       </c>
       <c r="Z8" t="n">
-        <v>174.8</v>
+        <v>111.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>548.6</v>
+        <v>172.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.6318</v>
+        <v>546.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.332</v>
+        <v>0.6216</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0065</v>
+        <v>0.366</v>
       </c>
       <c r="AE8" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.0171</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.0126</v>
+      </c>
+      <c r="AK8" t="n">
         <v>0.0072</v>
       </c>
-      <c r="AF8" t="n">
-        <v>0.0149</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0.0117</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0.0068</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0.0073</v>
+      <c r="AL8" t="n">
+        <v>0.005</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>eye</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>EU_CLP</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>native</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>nan0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1044</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>386</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>0.3697</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.7655999999999999</v>
-      </c>
       <c r="K9" t="n">
-        <v>0.0026</v>
+        <v>0.7577</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6822</v>
+        <v>0.0034</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0083</v>
+        <v>0.6745</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6188</v>
+        <v>0.0091</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0067</v>
+        <v>0.6096</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8056</v>
+        <v>0.0068</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7122000000000001</v>
+        <v>0.8006</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6836</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5653</v>
+        <v>0.6725</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8465</v>
+        <v>0.5575</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4315</v>
+        <v>0.8407</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7059</v>
+        <v>0.417</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7425</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>218.2</v>
+        <v>0.736</v>
       </c>
       <c r="Y9" t="n">
-        <v>101</v>
+        <v>215.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>167.8</v>
+        <v>104.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>557</v>
+        <v>170.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.6447000000000001</v>
+        <v>553.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.333</v>
+        <v>0.6377</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0027</v>
+        <v>0.351</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.0044</v>
+        <v>0.0028</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.0062</v>
+        <v>0.0045</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0101</v>
+        <v>0.0064</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0052</v>
+        <v>0.0098</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.005</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.0044</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0035</v>
+        <v>0.0045</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0037</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>skin</t>
-        </is>
-      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UN_GHS</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>EU_CLP</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>nan0</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>615</v>
-      </c>
       <c r="H10" t="n">
-        <v>371</v>
+        <v>1044</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6032999999999999</v>
+        <v>386</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6882</v>
+        <v>0.3697</v>
       </c>
       <c r="K10" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.7504999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7567</v>
+        <v>0.0049</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0126</v>
+        <v>0.6647</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7433</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0091</v>
+        <v>0.5978</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5477</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6455</v>
+        <v>0.7942</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7050999999999999</v>
+        <v>0.696</v>
       </c>
       <c r="S10" t="n">
-        <v>0.786</v>
+        <v>0.659</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5</v>
+        <v>0.5472</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2982</v>
+        <v>0.8337</v>
       </c>
       <c r="V10" t="n">
-        <v>0.643</v>
+        <v>0.3987</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6725</v>
+        <v>0.6904</v>
       </c>
       <c r="X10" t="n">
-        <v>291.6</v>
+        <v>0.7278</v>
       </c>
       <c r="Y10" t="n">
-        <v>122</v>
+        <v>211.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>79.40000000000001</v>
+        <v>109.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>122</v>
+        <v>174.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.7844</v>
+        <v>548.6</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.316</v>
+        <v>0.6318</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0176</v>
+        <v>0.332</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0129</v>
+        <v>0.0065</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.0095</v>
+        <v>0.0072</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0123</v>
+        <v>0.0149</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0203</v>
+        <v>0.0111</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0255</v>
+        <v>0.0117</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0125</v>
+        <v>0.0152</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0116</v>
+        <v>0.0068</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.0073</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>skin</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UN_GHS</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>EU_CLP</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>nan0</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>615</v>
-      </c>
       <c r="H11" t="n">
-        <v>371</v>
+        <v>1044</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6032999999999999</v>
+        <v>386</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7334000000000001</v>
+        <v>0.3697</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0064</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7875</v>
+        <v>0.0026</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0064</v>
+        <v>0.6822</v>
       </c>
       <c r="N11" t="n">
-        <v>0.7679</v>
+        <v>0.0083</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0065</v>
+        <v>0.6188</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5881</v>
+        <v>0.0067</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.678</v>
+        <v>0.8056</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7267</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.6836</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5344</v>
+        <v>0.5653</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3642</v>
+        <v>0.8465</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6742</v>
+        <v>0.4315</v>
       </c>
       <c r="W11" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7059</v>
       </c>
       <c r="X11" t="n">
-        <v>302</v>
+        <v>0.7425</v>
       </c>
       <c r="Y11" t="n">
-        <v>113.6</v>
+        <v>218.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="AA11" t="n">
-        <v>130.4</v>
+        <v>167.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.7906</v>
+        <v>557</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.366</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.013</v>
+        <v>0.333</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0094</v>
+        <v>0.0027</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0071</v>
+        <v>0.0044</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0062</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0155</v>
+        <v>0.0101</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0184</v>
+        <v>0.0052</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0091</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0083</v>
+        <v>0.0044</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.0035</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>skin</t>
-        </is>
-      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UN_GHS</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>EU_CLP</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>native</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>615</v>
-      </c>
       <c r="H12" t="n">
-        <v>371</v>
+        <v>1044</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6032999999999999</v>
+        <v>386</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6992</v>
+        <v>0.3697</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0116</v>
+        <v>0.7509</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7633</v>
+        <v>0.0034</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0155</v>
+        <v>0.6659</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7477</v>
+        <v>0.0081</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0067</v>
+        <v>0.6041</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5527</v>
+        <v>0.0054</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6502</v>
+        <v>0.797</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7078</v>
+        <v>0.7005</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7925</v>
+        <v>0.6647</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3082</v>
+        <v>0.8359</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6475</v>
+        <v>0.4076</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6774</v>
+        <v>0.6949</v>
       </c>
       <c r="X12" t="n">
-        <v>294</v>
+        <v>0.7316</v>
       </c>
       <c r="Y12" t="n">
-        <v>121.4</v>
+        <v>213.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="AA12" t="n">
-        <v>122.6</v>
+        <v>172.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.7875</v>
+        <v>550</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.383</v>
+        <v>0.6358</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0116</v>
+        <v>0.325</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.0053</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.0061</v>
+        <v>0.0046</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.0113</v>
+        <v>0.0128</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.0147</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.017</v>
+        <v>0.0115</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.0081</v>
+        <v>0.0102</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.0078</v>
+        <v>0.0041</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0.0053</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>0</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>skin</t>
-        </is>
-      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UN_GHS</t>
+          <t>eye</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>EU_CLP</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>native</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>615</v>
-      </c>
       <c r="H13" t="n">
-        <v>371</v>
+        <v>1044</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6032999999999999</v>
+        <v>386</v>
       </c>
       <c r="J13" t="n">
-        <v>0.735</v>
+        <v>0.3697</v>
       </c>
       <c r="K13" t="n">
+        <v>0.7634</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.713</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6814</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.5705</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.8435</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.4322</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>103</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>165.8</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>555</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.6417</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="AH13" t="n">
         <v>0.0107</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.7899</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0097</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.7659</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.0115</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.5916</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.6788</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.7289</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.8070000000000001</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.5434</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.3641</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.6752</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0.7024</v>
-      </c>
-      <c r="X13" t="n">
-        <v>299.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>111.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>132.6</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0.7903</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.0218</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0.0164</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.0119</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0.0231</v>
-      </c>
       <c r="AI13" t="n">
-        <v>0.0326</v>
+        <v>0.0058</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.0159</v>
+        <v>0.01</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.0149</v>
+        <v>0.0052</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.0044</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>0</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>skin</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>EU_CLP+K_REACH+US_OSHA</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>UN_GHS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>nan0</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>1059</v>
-      </c>
       <c r="H14" t="n">
-        <v>356</v>
+        <v>615</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3362</v>
+        <v>371</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7547</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.6882</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6393</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0055</v>
+        <v>0.7567</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5635</v>
+        <v>0.0126</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0124</v>
+        <v>0.7433</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8041</v>
+        <v>0.0091</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6838</v>
+        <v>0.5477</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6163</v>
+        <v>0.6455</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5191</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8361</v>
+        <v>0.786</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3726</v>
+        <v>0.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6776</v>
+        <v>0.2982</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7296</v>
+        <v>0.643</v>
       </c>
       <c r="X14" t="n">
-        <v>184.8</v>
+        <v>0.6725</v>
       </c>
       <c r="Y14" t="n">
-        <v>115.2</v>
+        <v>291.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>171.2</v>
+        <v>122</v>
       </c>
       <c r="AA14" t="n">
-        <v>587.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.5931</v>
+        <v>122</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.298</v>
+        <v>0.7844</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.0075</v>
+        <v>0.316</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0097</v>
+        <v>0.0176</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.0192</v>
+        <v>0.0129</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.011</v>
+        <v>0.0095</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.0118</v>
+        <v>0.0123</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.0204</v>
+        <v>0.0203</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0089</v>
+        <v>0.0255</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.0094</v>
+        <v>0.0125</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.0116</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>skin</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>EU_CLP+K_REACH+US_OSHA</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>UN_GHS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>nan0</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>1059</v>
-      </c>
       <c r="H15" t="n">
-        <v>356</v>
+        <v>615</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3362</v>
+        <v>371</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0041</v>
+        <v>0.7334000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.645</v>
+        <v>0.0064</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0046</v>
+        <v>0.7875</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5725</v>
+        <v>0.0064</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0115</v>
+        <v>0.7679</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8078</v>
+        <v>0.0065</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6902</v>
+        <v>0.5881</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6252</v>
+        <v>0.678</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5281</v>
+        <v>0.7267</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8395</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3852</v>
+        <v>0.5344</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6838</v>
+        <v>0.3642</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7348</v>
+        <v>0.6742</v>
       </c>
       <c r="X15" t="n">
-        <v>188</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>112.8</v>
+        <v>302</v>
       </c>
       <c r="Z15" t="n">
-        <v>168</v>
+        <v>113.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>590.2</v>
+        <v>69</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.6213</v>
+        <v>130.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.349</v>
+        <v>0.7906</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.0065</v>
+        <v>0.366</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.0163</v>
+        <v>0.0094</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.0095</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.0183</v>
+        <v>0.0155</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.0184</v>
       </c>
       <c r="AK15" t="n">
+        <v>0.0091</v>
+      </c>
+      <c r="AL15" t="n">
         <v>0.0083</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>0</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>skin</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>EU_CLP+K_REACH+US_OSHA</t>
-        </is>
-      </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>UN_GHS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>native</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>CT_A0</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>1059</v>
-      </c>
       <c r="H16" t="n">
-        <v>356</v>
+        <v>615</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3362</v>
+        <v>371</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7612</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0071</v>
+        <v>0.6992</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6481</v>
+        <v>0.0116</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0047</v>
+        <v>0.7633</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5561</v>
+        <v>0.0155</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0066</v>
+        <v>0.7477</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8034</v>
+        <v>0.0067</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.6797</v>
+        <v>0.5527</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6146</v>
+        <v>0.6502</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5079</v>
+        <v>0.7078</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8387</v>
+        <v>0.7925</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3655</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6733</v>
+        <v>0.3082</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7275</v>
+        <v>0.6475</v>
       </c>
       <c r="X16" t="n">
-        <v>180.8</v>
+        <v>0.6774</v>
       </c>
       <c r="Y16" t="n">
-        <v>113.4</v>
+        <v>294</v>
       </c>
       <c r="Z16" t="n">
-        <v>175.2</v>
+        <v>121.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>589.6</v>
+        <v>77</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.6057</v>
+        <v>122.6</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.298</v>
+        <v>0.7875</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.0025</v>
+        <v>0.383</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.004</v>
+        <v>0.0116</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.0064</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.0098</v>
+        <v>0.0061</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.0052</v>
+        <v>0.0113</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.0077</v>
+        <v>0.0147</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.0041</v>
+        <v>0.017</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.0032</v>
+        <v>0.0081</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0.0078</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>0</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>제형</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>skin</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>UN_GHS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CT_권고</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>615</v>
+      </c>
+      <c r="I17" t="n">
+        <v>371</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0107</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.7899</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.7659</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5916</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6788</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.7289</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.5434</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.6752</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.7024</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>299.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>111.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.7903</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0.0218</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0.0231</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0.0149</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>0</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>UN_GHS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>CT_A0</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>615</v>
+      </c>
+      <c r="I18" t="n">
+        <v>371</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7004</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.7616000000000001</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.6484</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.7072000000000001</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.7865</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.6457000000000001</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.6748</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>120.8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.7849</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.0128</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0.0289</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0.0139</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>0</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>UN_GHS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CT_권고</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>615</v>
+      </c>
+      <c r="I19" t="n">
+        <v>371</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6032999999999999</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.7357</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.7907</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.7652</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5915</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.6784</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7288</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.8054</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.6748</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.7018</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>298.8</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>132.8</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.7863</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.0113</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>0</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>EU_CLP+K_REACH+US_OSHA</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>제형집계+물성+CT</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>nan0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CT_A0</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1059</v>
+      </c>
+      <c r="I20" t="n">
+        <v>356</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.7547</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5635</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.0124</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.8041</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.6838</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.6163</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.5191</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.8361</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.6776</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.7296</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>184.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>171.2</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>587.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.5931</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0.0204</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.0089</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0.0094</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>0</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EU_CLP+K_REACH+US_OSHA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>nan0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CT_권고</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1059</v>
+      </c>
+      <c r="I21" t="n">
+        <v>356</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.7697000000000001</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.8078</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.6902</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.6252</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5281</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.8395</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.6838</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.7348</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>188</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>168</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>590.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0.009900000000000001</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.0095</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.0183</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0.0083</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>EU_CLP+K_REACH+US_OSHA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>native</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CT_A0</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1059</v>
+      </c>
+      <c r="I22" t="n">
+        <v>356</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.7612</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.6481</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5561</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.6797</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.6146</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.5079</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.8387</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.7275</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>180.8</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>175.2</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>589.6</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.6057</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0.0032</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>EU_CLP+K_REACH+US_OSHA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>native</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>CT_권고</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H23" t="n">
         <v>1059</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I23" t="n">
         <v>356</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J23" t="n">
         <v>0.3362</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K23" t="n">
         <v>0.7754</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L23" t="n">
         <v>0.0031</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M23" t="n">
         <v>0.656</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N23" t="n">
         <v>0.0051</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O23" t="n">
         <v>0.5804</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P23" t="n">
         <v>0.0046</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q23" t="n">
         <v>0.8126</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R23" t="n">
         <v>0.6965</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S23" t="n">
         <v>0.6371</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T23" t="n">
         <v>0.5331</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U23" t="n">
         <v>0.8461</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V23" t="n">
         <v>0.3985</v>
       </c>
-      <c r="V17" t="n">
+      <c r="W23" t="n">
         <v>0.6896</v>
       </c>
-      <c r="W17" t="n">
+      <c r="X23" t="n">
         <v>0.7409</v>
       </c>
-      <c r="X17" t="n">
+      <c r="Y23" t="n">
         <v>189.8</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Z23" t="n">
         <v>108.2</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AA23" t="n">
         <v>166.2</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AB23" t="n">
         <v>594.8</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AC23" t="n">
         <v>0.6338</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AD23" t="n">
         <v>0.338</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AE23" t="n">
         <v>0.0038</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AF23" t="n">
         <v>0.0037</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AG23" t="n">
         <v>0.0104</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AH23" t="n">
         <v>0.0075</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AI23" t="n">
         <v>0.008</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AJ23" t="n">
         <v>0.008200000000000001</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AK23" t="n">
         <v>0.0033</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AL23" t="n">
         <v>0.0041</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EU_CLP+K_REACH+US_OSHA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>CT_A0</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>1059</v>
+      </c>
+      <c r="I24" t="n">
+        <v>356</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7619</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0062</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.6472</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.008399999999999999</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.8075</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.6868</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.5174</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.8427</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>184.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>171.8</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>592.4</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0.6022</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.0057</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.0104</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.0051</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>제형</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>skin</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EU_CLP+K_REACH+US_OSHA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>제형집계+물성+CT</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>native_복원</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>CT_권고</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>1059</v>
+      </c>
+      <c r="I25" t="n">
+        <v>356</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.7726</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.0041</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6538</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5750999999999999</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8097</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.6924</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.6299</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.8424</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.6858</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.7371</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>188.4</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>110.8</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>167.6</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>592.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0.6193</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.0144</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.0066</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK17"/>
+  <autoFilter ref="A1:AL25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>